--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_mat_a_2020_o_higgins.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_mat_a_2020_o_higgins.xlsx
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:17</t>
+    <t xml:space="preserve">2026-09-24 01:07</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -675,19 +675,19 @@
         <v>16</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>-0.22</v>
+        <v>-0.21</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>0.02</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>-0.24</v>
+        <v>-0.22</v>
       </c>
     </row>
     <row r="9">
@@ -698,16 +698,16 @@
         <v>16</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>0.56</v>
+        <v>0.55</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>0.04</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>0.52</v>
@@ -721,19 +721,19 @@
         <v>16</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>-0.41</v>
+        <v>-0.42</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>-0.41</v>
+        <v>-0.42</v>
       </c>
     </row>
     <row r="11">
@@ -747,16 +747,16 @@
         <v>-0.55</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>-0.05</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>-0.49</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="12">
@@ -796,13 +796,13 @@
         <v>33</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>-0.12</v>
+        <v>-0.11</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>-0.14</v>
+        <v>-0.15</v>
       </c>
     </row>
     <row r="14">
@@ -822,7 +822,7 @@
         <v>-0.18</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>0.14</v>
@@ -845,7 +845,7 @@
         <v>0.15</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>-0.21</v>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_mat_a_2020_o_higgins.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_mat_a_2020_o_higgins.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Migración</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Saldo migratorio</t>
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 01:07</t>
+    <t xml:space="preserve">2026-10-01 23:19</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_mat_a_2020_o_higgins.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_mat_a_2020_o_higgins.xlsx
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:19</t>
+    <t xml:space="preserve">2026-10-05 19:43</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
